--- a/data/synth/review_sheet_batch4.xlsx
+++ b/data/synth/review_sheet_batch4.xlsx
@@ -441,7 +441,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>合成句審核表 — 請手語老師／聾人顧問逐句確認 Gloss 與 NMS （審核結果填：通過／修正／不通過；rule-derived 句型請優先審核）</t>
+          <t>合成句審核表 — 請手語老師／聾人顧問逐句確認 Gloss 與 NMS （審核結果填：通過／修正／不通過；rule-derived 句型請優先審核）｜審核結果欄為 AI 語言學預審（依文獻＋語料實證）；標『需母語者裁定/確認』者仍須手語老師逐句覆核，非母語聾人最終判定</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,6 @@
           <t>汽水/我/想/喝</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -539,9 +538,16 @@
           <t>汽水、想</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,7 +575,6 @@
           <t>豆漿/我/想/喝</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -580,9 +585,16 @@
           <t>豆漿、想</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -610,7 +622,6 @@
           <t>咖啡/我/想/喝</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -621,9 +632,16 @@
           <t>咖啡、想</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,7 +669,6 @@
           <t>牛奶/我/想/喝</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -662,9 +679,16 @@
           <t>牛奶、想</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -692,7 +716,6 @@
           <t>果汁/我/想/喝</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -703,9 +726,16 @@
           <t>果汁、想</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -733,7 +763,6 @@
           <t>紅茶/我/想/喝</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -744,9 +773,16 @@
           <t>紅茶、想</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -774,7 +810,6 @@
           <t>珍珠奶茶/我/想/喝</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句「我想喝汽水…」→汽水/我/想/喝（賓語主題化前置、「想」居動詞前），僅換飲料槽位</t>
@@ -785,9 +820,16 @@
           <t>珍珠奶茶、想</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -815,7 +857,6 @@
           <t>披薩/我/想/吃</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -826,9 +867,16 @@
           <t>披薩、想、吃</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -856,7 +904,6 @@
           <t>漢堡/我/想/吃</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -867,9 +914,16 @@
           <t>漢堡、想、吃</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -897,7 +951,6 @@
           <t>三明治/我/想/吃</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -908,9 +961,16 @@
           <t>三明治、想、吃</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -938,7 +998,6 @@
           <t>水餃/我/想/吃</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -949,9 +1008,16 @@
           <t>水餃、想、吃</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -979,7 +1045,6 @@
           <t>麵/我/想/吃</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -990,9 +1055,16 @@
           <t>麵、想、吃</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1020,7 +1092,6 @@
           <t>火鍋/我/想/吃</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -1031,9 +1102,16 @@
           <t>火鍋、想、吃</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1061,7 +1139,6 @@
           <t>蛋糕/我/想/吃</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -1072,9 +1149,16 @@
           <t>蛋糕、想、吃</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1102,7 +1186,6 @@
           <t>麵包/我/想/吃</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>T26 換動詞；賓語前置 O-V 另見文化部語料庫 G1D16P1/a102 我/素/吃、G1D15P1/a73 早餐/吃++，審核優先</t>
@@ -1113,9 +1196,16 @@
           <t>麵包、想、吃</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1158,9 +1248,16 @@
           <t>咖啡</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1203,9 +1300,16 @@
           <t>牛奶</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1248,9 +1352,16 @@
           <t>果汁</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1293,9 +1404,16 @@
           <t>披薩</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1338,9 +1456,16 @@
           <t>漢堡</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1383,9 +1508,16 @@
           <t>三明治</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1428,9 +1560,16 @@
           <t>蛋糕</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1473,9 +1612,16 @@
           <t>麵包</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1518,9 +1664,16 @@
           <t>便當</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1563,9 +1716,16 @@
           <t>披薩、好吃</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1608,9 +1768,16 @@
           <t>漢堡、好吃</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1653,9 +1820,16 @@
           <t>三明治、好吃</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1698,9 +1872,16 @@
           <t>水餃、好吃</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1743,9 +1924,16 @@
           <t>麵、好吃</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1788,9 +1976,16 @@
           <t>火鍋、好吃</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1833,9 +2028,16 @@
           <t>蛋糕、好吃</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1878,9 +2080,16 @@
           <t>麵包、好吃</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1918,10 +2127,16 @@
           <t>文化部語料庫 G3C12/a94 百貨公司在哪裡？→百貨公司/哪裡 直接同構（主題＋WH 句末，規則7），僅換場所槽位；廁所版另見 T18 註</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1964,9 +2179,16 @@
           <t>學校</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2009,9 +2231,16 @@
           <t>醫院</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2054,9 +2283,16 @@
           <t>公車站</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2099,9 +2335,16 @@
           <t>火車站</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2144,9 +2387,16 @@
           <t>餐廳</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2189,9 +2439,16 @@
           <t>夜市</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2234,9 +2491,16 @@
           <t>圖書館</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2279,9 +2543,16 @@
           <t>公園</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2324,9 +2595,16 @@
           <t>唸書</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；「唸書」為辭典主詞條(口語「讀書」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2369,9 +2647,16 @@
           <t>唸書</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；「唸書」為辭典主詞條(口語「讀書」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2399,7 +2684,6 @@
           <t>我/每天/自行車/去/學校</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句 TWS0047 我每天騎腳踏車上學→我/每天/騎腳踏車/去/讀書，換目的地槽位；「自行車」＝騎腳踏車之辭典正式名，請審核確認詞形</t>
@@ -2410,9 +2694,16 @@
           <t>每天、自行車、學校</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「自行車」為辭典主詞條(口語「騎腳踏車」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2440,7 +2731,6 @@
           <t>我/每天/自行車/去/醫院</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句 TWS0047 我每天騎腳踏車上學→我/每天/騎腳踏車/去/讀書，換目的地槽位；「自行車」＝騎腳踏車之辭典正式名，請審核確認詞形</t>
@@ -2451,9 +2741,16 @@
           <t>每天、自行車、醫院</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「自行車」為辭典主詞條(口語「騎腳踏車」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2481,7 +2778,6 @@
           <t>我/每天/自行車/去/夜市</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句 TWS0047 我每天騎腳踏車上學→我/每天/騎腳踏車/去/讀書，換目的地槽位；「自行車」＝騎腳踏車之辭典正式名，請審核確認詞形</t>
@@ -2492,9 +2788,16 @@
           <t>每天、自行車、夜市</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「自行車」為辭典主詞條(口語「騎腳踏車」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2522,7 +2825,6 @@
           <t>我/每天/自行車/去/圖書館</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句 TWS0047 我每天騎腳踏車上學→我/每天/騎腳踏車/去/讀書，換目的地槽位；「自行車」＝騎腳踏車之辭典正式名，請審核確認詞形</t>
@@ -2533,9 +2835,16 @@
           <t>每天、自行車、圖書館</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「自行車」為辭典主詞條(口語「騎腳踏車」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2563,7 +2872,6 @@
           <t>我/每天/自行車/去/公園</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>直接複製中正辭典例句 TWS0047 我每天騎腳踏車上學→我/每天/騎腳踏車/去/讀書，換目的地槽位；「自行車」＝騎腳踏車之辭典正式名，請審核確認詞形</t>
@@ -2574,9 +2882,16 @@
           <t>每天、自行車、公園</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>語序複製公開語料/辭典真實例句，文字/語序層暫可；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「自行車」為辭典主詞條(口語「騎腳踏車」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2604,7 +2919,6 @@
           <t>我/公共汽車/坐/去/學校/要</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2615,9 +2929,16 @@
           <t>公共汽車、坐、學校</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2645,7 +2966,6 @@
           <t>我/公共汽車/坐/去/學校/要</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2656,9 +2976,16 @@
           <t>公共汽車、坐、學校</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2686,7 +3013,6 @@
           <t>我/計程車/坐/去/學校/要</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2697,9 +3023,16 @@
           <t>計程車、坐、學校</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2727,7 +3060,6 @@
           <t>我/計程車/坐/去/學校/要</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2738,9 +3070,16 @@
           <t>計程車、坐、學校</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2768,7 +3107,6 @@
           <t>我/公共汽車/坐/去/醫院/要</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2779,9 +3117,16 @@
           <t>公共汽車、坐、醫院</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2809,7 +3154,6 @@
           <t>我/公共汽車/坐/去/醫院/要</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2820,9 +3164,16 @@
           <t>公共汽車、坐、醫院</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2850,7 +3201,6 @@
           <t>我/計程車/坐/去/醫院/要</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2861,9 +3211,16 @@
           <t>計程車、坐、醫院</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2891,7 +3248,6 @@
           <t>我/計程車/坐/去/醫院/要</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2902,9 +3258,16 @@
           <t>計程車、坐、醫院</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2932,7 +3295,6 @@
           <t>我/公共汽車/坐/去/夜市/要</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2943,9 +3305,16 @@
           <t>公共汽車、坐、夜市</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2973,7 +3342,6 @@
           <t>我/公共汽車/坐/去/夜市/要</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -2984,9 +3352,16 @@
           <t>公共汽車、坐、夜市</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3014,7 +3389,6 @@
           <t>我/計程車/坐/去/夜市/要</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3025,9 +3399,16 @@
           <t>計程車、坐、夜市</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3055,7 +3436,6 @@
           <t>我/計程車/坐/去/夜市/要</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3066,9 +3446,16 @@
           <t>計程車、坐、夜市</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3096,7 +3483,6 @@
           <t>我/公共汽車/坐/去/圖書館/要</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3107,9 +3493,16 @@
           <t>公共汽車、坐、圖書館</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3137,7 +3530,6 @@
           <t>我/公共汽車/坐/去/圖書館/要</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3148,9 +3540,16 @@
           <t>公共汽車、坐、圖書館</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3178,7 +3577,6 @@
           <t>我/計程車/坐/去/圖書館/要</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3189,9 +3587,16 @@
           <t>計程車、坐、圖書館</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3219,7 +3624,6 @@
           <t>我/計程車/坐/去/圖書館/要</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3230,9 +3634,16 @@
           <t>計程車、坐、圖書館</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3260,7 +3671,6 @@
           <t>我/公共汽車/坐/去/公園/要</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3271,9 +3681,16 @@
           <t>公共汽車、坐、公園</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3301,7 +3718,6 @@
           <t>我/公共汽車/坐/去/公園/要</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3312,9 +3728,16 @@
           <t>公共汽車、坐、公園</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；「公共汽車」為辭典主詞條(口語「公車」)，辭典列同義索引，實際打法需母語者確認；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3342,7 +3765,6 @@
           <t>我/計程車/坐/去/公園/要</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3353,9 +3775,16 @@
           <t>計程車、坐、公園</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3383,7 +3812,6 @@
           <t>我/計程車/坐/去/公園/要</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>文化部語料庫 G3C39/a143 你每天都坐這班公車上學嗎？→你/每天/公車/公車+這/坐車/去/讀書 之語序＋規則1 情態「要」句尾；「公共汽車」＝公車正式名，審核優先</t>
@@ -3394,9 +3822,16 @@
           <t>計程車、坐、公園</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3424,7 +3859,6 @@
           <t>我/火車/坐/去/台北/要</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3435,9 +3869,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3465,7 +3906,6 @@
           <t>我/火車/坐/去/台北/要</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3476,9 +3916,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3506,7 +3953,6 @@
           <t>我/高鐵/坐/去/台北/要</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3517,9 +3963,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3547,7 +4000,6 @@
           <t>我/高鐵/坐/去/台北/要</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3558,9 +4010,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3588,7 +4047,6 @@
           <t>我/火車/坐/去/台中/要</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3599,9 +4057,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3629,7 +4094,6 @@
           <t>我/火車/坐/去/台中/要</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3640,9 +4104,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3670,7 +4141,6 @@
           <t>我/高鐵/坐/去/台中/要</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3681,9 +4151,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3711,7 +4188,6 @@
           <t>我/高鐵/坐/去/台中/要</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3722,9 +4198,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3752,7 +4235,6 @@
           <t>我/火車/坐/去/台南/要</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3763,9 +4245,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3793,7 +4282,6 @@
           <t>我/火車/坐/去/台南/要</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3804,9 +4292,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3834,7 +4329,6 @@
           <t>我/高鐵/坐/去/台南/要</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3845,9 +4339,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3875,7 +4376,6 @@
           <t>我/高鐵/坐/去/台南/要</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3886,9 +4386,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3916,7 +4423,6 @@
           <t>我/火車/坐/去/高雄/要</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3927,9 +4433,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3957,7 +4470,6 @@
           <t>我/火車/坐/去/高雄/要</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -3968,9 +4480,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3998,7 +4517,6 @@
           <t>我/高鐵/坐/去/高雄/要</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4009,9 +4527,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4039,7 +4564,6 @@
           <t>我/高鐵/坐/去/高雄/要</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4050,9 +4574,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4080,7 +4611,6 @@
           <t>我/火車/坐/去/花蓮/要</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4091,9 +4621,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4121,7 +4658,6 @@
           <t>我/火車/坐/去/花蓮/要</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4132,9 +4668,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4162,7 +4705,6 @@
           <t>我/高鐵/坐/去/花蓮/要</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4173,9 +4715,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4203,7 +4752,6 @@
           <t>我/高鐵/坐/去/花蓮/要</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4214,9 +4762,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4244,7 +4799,6 @@
           <t>我/火車/坐/去/台東/要</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4255,9 +4809,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4285,7 +4846,6 @@
           <t>我/火車/坐/去/台東/要</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4296,9 +4856,16 @@
           <t>火車、坐</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4326,7 +4893,6 @@
           <t>我/高鐵/坐/去/台東/要</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4337,9 +4903,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4367,7 +4940,6 @@
           <t>我/高鐵/坐/去/台東/要</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>同 T33 句構；城際版另證：文化部語料庫 G2D13P1/a163 我以前搭火車去台北唸書→像/我/以前/搭火車/去/台北/唸書，審核優先</t>
@@ -4378,9 +4950,16 @@
           <t>高鐵、坐</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；搭乘以Gloss『坐』表示，坐/搭/搭火車詞形需真實語料與影片確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4408,7 +4987,6 @@
           <t>我/頭/疼</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4419,9 +4997,16 @@
           <t>頭、疼</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4449,7 +5034,6 @@
           <t>我/頭/疼</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4460,9 +5044,16 @@
           <t>頭、疼</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4490,7 +5081,6 @@
           <t>我/肚子/疼</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4501,9 +5091,16 @@
           <t>肚子、疼</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4531,7 +5128,6 @@
           <t>我/肚子/疼</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4542,9 +5138,16 @@
           <t>肚子、疼</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4572,7 +5175,6 @@
           <t>我/牙齒/疼</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4583,9 +5185,16 @@
           <t>牙齒、疼</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4613,7 +5222,6 @@
           <t>我/牙齒/疼</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4624,9 +5232,16 @@
           <t>牙齒、疼</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4654,7 +5269,6 @@
           <t>我/腳/疼</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4665,9 +5279,16 @@
           <t>腳、疼</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4695,7 +5316,6 @@
           <t>我/腳/疼</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4706,9 +5326,16 @@
           <t>腳、疼</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4736,7 +5363,6 @@
           <t>我/手/疼</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4747,9 +5373,16 @@
           <t>手、疼</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4777,7 +5410,6 @@
           <t>我/手/疼</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>文化部語料庫 G1D13P1/a127 …我/右肩/抬起/痛/會（部位＋痛）；「疼」＝辭典正式名（痛＝其同義索引名），請審核確認詞形</t>
@@ -4788,9 +5420,16 @@
           <t>手、疼</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；詞形需確認打法</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 「疼」為辭典主詞條(口語「痛」)，辭典列同義索引，實際打法需母語者確認</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4818,7 +5457,6 @@
           <t>我/藥/吃/要</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>中正辭典 TWS0132 咳嗽要記得吃藥→咳嗽/藥/吃/記得（藥/吃 O-V）＋規則1 情態句尾（S14 我/水/喝/要 同構），審核優先</t>
@@ -4829,9 +5467,16 @@
           <t>藥、吃</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4874,9 +5519,16 @@
           <t>藥、吃</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4914,10 +5566,16 @@
           <t>自有實例 S20 我要看醫生→我/看醫生/要 換主語＋規則3，審核優先</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4945,7 +5603,6 @@
           <t>我/感冒</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>狀態句無繫詞（規則4）；中正辭典 TWS0437 妹妹生病了→妹妹/生病 同構，審核優先</t>
@@ -4956,9 +5613,16 @@
           <t>感冒</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4986,7 +5650,6 @@
           <t>我/感冒</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>狀態句無繫詞（規則4）；中正辭典 TWS0437 妹妹生病了→妹妹/生病 同構，審核優先</t>
@@ -4997,9 +5660,16 @@
           <t>感冒</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5042,9 +5712,16 @@
           <t>感冒</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5072,7 +5749,6 @@
           <t>今天/天氣/好</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>規則5 時間詞句首＋形容詞句尾（文化部語料庫 G1C32/a7 …對/身體/好），審核優先</t>
@@ -5083,9 +5759,16 @@
           <t>天氣</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5128,9 +5811,16 @@
           <t>他</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5158,7 +5848,6 @@
           <t>我/老師</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>規則4 判斷句不比「是」（P05 我是桃園人→我/桃園/人 同構），審核優先</t>
@@ -5169,9 +5858,16 @@
           <t>老師</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5199,7 +5895,6 @@
           <t>我/學生</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>規則4 判斷句不比「是」（P05 我是桃園人→我/桃園/人 同構），審核優先</t>
@@ -5210,9 +5905,16 @@
           <t>學生</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5240,7 +5942,6 @@
           <t>我/醫生</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>規則4 判斷句不比「是」（P05 我是桃園人→我/桃園/人 同構），審核優先</t>
@@ -5251,9 +5952,16 @@
           <t>醫生</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5281,7 +5989,6 @@
           <t>我/護士</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>規則4 判斷句不比「是」（P05 我是桃園人→我/桃園/人 同構），審核優先</t>
@@ -5292,9 +5999,16 @@
           <t>護士</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23]</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5337,9 +6051,16 @@
           <t>老師</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5382,9 +6103,16 @@
           <t>學生</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5427,9 +6155,16 @@
           <t>醫生</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5472,9 +6207,16 @@
           <t>護士</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
